--- a/Python/cleaning/setup misses.xlsx
+++ b/Python/cleaning/setup misses.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D6D5CD-505E-45EC-8840-3D38848B95F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEFAEFA-EEF7-41D5-8D7F-570BC409616F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Subject</t>
   </si>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t>10, 34, 44, 54, 96, 101, 137, 204, 210</t>
+  </si>
+  <si>
+    <t>73, 145</t>
+  </si>
+  <si>
+    <t>10, 18, 30, 41, 55, 58, 76, 79, 89, 92, 100, 104, 110, 116, 122, 131, 140, 147, 148, 161, 170, 174, 179, 189, 192, 195, 209, 24, 29, 60</t>
   </si>
 </sst>
 </file>
@@ -757,11 +763,13 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="54" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="6" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
@@ -1030,10 +1038,12 @@
       <c r="B51" s="6"/>
     </row>
     <row r="52" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B52" s="6"/>
+      <c r="B52" s="11" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="53" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
